--- a/media/exports/reports/2026-08/cash-payroll.xlsx
+++ b/media/exports/reports/2026-08/cash-payroll.xlsx
@@ -871,7 +871,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
+          <t>Period: August 2026 · Data status: Aug 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2332,7 +2332,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
+          <t>Period: August 2026 · Data status: Aug 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3054,7 +3054,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
+          <t>Period: August 2026 · Data status: Aug 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
